--- a/docks/UFO_Pinout.xlsx
+++ b/docks/UFO_Pinout.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="113">
   <si>
     <t xml:space="preserve">Назначение в проекте</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t xml:space="preserve">I2C SDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZZZ</t>
   </si>
   <si>
     <t xml:space="preserve">GPIO32</t>
@@ -982,555 +985,555 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="12" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="19" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="19" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="20" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="17" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="21" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="22" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="22" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="23" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="24" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="23" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="19" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="19" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="20" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="17" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="21" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="22" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="22" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="23" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="19" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="24" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="23" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="24" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="25" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="24" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="25" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="25" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="25" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="25" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="25" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="25" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="25" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="25" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="25" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="25" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="25" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="25" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="25" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="16" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="16" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="25" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="25" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="24" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="22" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="17" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="24" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="22" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="17" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="21" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="19" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="21" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1617,9 +1620,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>1535400</xdr:colOff>
+      <xdr:colOff>1535040</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>142560</xdr:rowOff>
+      <xdr:rowOff>142200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1632,8 +1635,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12079440" y="1260720"/>
-          <a:ext cx="1240200" cy="2444040"/>
+          <a:off x="12072600" y="1260720"/>
+          <a:ext cx="1239840" cy="2443680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1831,20 +1834,20 @@
   <dimension ref="B1:AJ33"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="10.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="11" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="6.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="3.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="27.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="3.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="6.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="2.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="23" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="28" style="1" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="30" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="30" style="1" width="10.7"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="37" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -2426,7 +2429,9 @@
       <c r="AJ11" s="44"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="65"/>
+      <c r="B12" s="65" t="s">
+        <v>36</v>
+      </c>
       <c r="C12" s="65"/>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -2454,7 +2459,7 @@
         <v>21</v>
       </c>
       <c r="Q12" s="54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R12" s="67" t="n">
         <v>6</v>
@@ -2464,7 +2469,7 @@
         <v>25</v>
       </c>
       <c r="U12" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V12" s="55" t="s">
         <v>21</v>
@@ -2485,11 +2490,11 @@
         <v>21</v>
       </c>
       <c r="AB12" s="56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AC12" s="56"/>
       <c r="AD12" s="65" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AE12" s="65"/>
       <c r="AF12" s="65"/>
@@ -2527,7 +2532,7 @@
         <v>21</v>
       </c>
       <c r="Q13" s="54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R13" s="67" t="n">
         <v>7</v>
@@ -2537,7 +2542,7 @@
         <v>24</v>
       </c>
       <c r="U13" s="54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V13" s="55" t="s">
         <v>21</v>
@@ -2558,7 +2563,7 @@
         <v>21</v>
       </c>
       <c r="AB13" s="56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC13" s="56"/>
       <c r="AD13" s="65"/>
@@ -2578,7 +2583,7 @@
       <c r="G14" s="43"/>
       <c r="H14" s="44"/>
       <c r="I14" s="69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J14" s="69"/>
       <c r="K14" s="46" t="s">
@@ -2600,7 +2605,7 @@
         <v>21</v>
       </c>
       <c r="Q14" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R14" s="71" t="n">
         <v>8</v>
@@ -2610,7 +2615,7 @@
         <v>23</v>
       </c>
       <c r="U14" s="72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V14" s="55" t="s">
         <v>21</v>
@@ -2625,20 +2630,20 @@
         <v>18</v>
       </c>
       <c r="Z14" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA14" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB14" s="56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC14" s="56"/>
       <c r="AD14" s="42"/>
       <c r="AE14" s="43"/>
       <c r="AF14" s="43"/>
       <c r="AG14" s="76" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AH14" s="43"/>
       <c r="AI14" s="43"/>
@@ -2646,7 +2651,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="77" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="77"/>
       <c r="D15" s="77"/>
@@ -2655,7 +2660,7 @@
       <c r="G15" s="77"/>
       <c r="H15" s="77"/>
       <c r="I15" s="69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J15" s="69"/>
       <c r="K15" s="46" t="s">
@@ -2677,7 +2682,7 @@
         <v>21</v>
       </c>
       <c r="Q15" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R15" s="71" t="n">
         <v>9</v>
@@ -2687,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="U15" s="54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V15" s="55" t="s">
         <v>21</v>
@@ -2708,26 +2713,26 @@
         <v>21</v>
       </c>
       <c r="AB15" s="56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC15" s="56"/>
       <c r="AD15" s="78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AE15" s="78"/>
       <c r="AF15" s="78"/>
       <c r="AG15" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH15" s="78" t="s">
         <v>55</v>
-      </c>
-      <c r="AH15" s="78" t="s">
-        <v>54</v>
       </c>
       <c r="AI15" s="78"/>
       <c r="AJ15" s="78"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="77"/>
       <c r="D16" s="77"/>
@@ -2756,7 +2761,7 @@
         <v>21</v>
       </c>
       <c r="Q16" s="54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R16" s="80" t="n">
         <v>10</v>
@@ -2766,7 +2771,7 @@
         <v>21</v>
       </c>
       <c r="U16" s="54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V16" s="55" t="s">
         <v>21</v>
@@ -2787,7 +2792,7 @@
         <v>21</v>
       </c>
       <c r="AB16" s="56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC16" s="56"/>
       <c r="AD16" s="78"/>
@@ -2800,7 +2805,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="77"/>
       <c r="D17" s="77"/>
@@ -2809,10 +2814,10 @@
       <c r="G17" s="77"/>
       <c r="H17" s="77"/>
       <c r="I17" s="69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J17" s="81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K17" s="46" t="s">
         <v>21</v>
@@ -2833,7 +2838,7 @@
         <v>21</v>
       </c>
       <c r="Q17" s="54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R17" s="82" t="n">
         <v>11</v>
@@ -2843,7 +2848,7 @@
         <v>20</v>
       </c>
       <c r="U17" s="54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V17" s="55" t="s">
         <v>21</v>
@@ -2855,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="Y17" s="83" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z17" s="46" t="s">
         <v>21</v>
@@ -2869,7 +2874,7 @@
       <c r="AE17" s="43"/>
       <c r="AF17" s="43"/>
       <c r="AG17" s="76" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AH17" s="43"/>
       <c r="AI17" s="43"/>
@@ -2884,19 +2889,19 @@
       <c r="G18" s="43"/>
       <c r="H18" s="44"/>
       <c r="I18" s="69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J18" s="81" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K18" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L18" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M18" s="84" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N18" s="73" t="s">
         <v>17</v>
@@ -2908,7 +2913,7 @@
         <v>21</v>
       </c>
       <c r="Q18" s="72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R18" s="85" t="n">
         <v>12</v>
@@ -2918,7 +2923,7 @@
         <v>19</v>
       </c>
       <c r="U18" s="72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V18" s="55" t="s">
         <v>21</v>
@@ -2927,26 +2932,26 @@
         <v>2</v>
       </c>
       <c r="X18" s="87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y18" s="84" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z18" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA18" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB18" s="56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC18" s="56"/>
       <c r="AD18" s="42"/>
       <c r="AE18" s="43"/>
       <c r="AF18" s="43"/>
       <c r="AG18" s="76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH18" s="43"/>
       <c r="AI18" s="43"/>
@@ -2954,7 +2959,7 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="77" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" s="77"/>
       <c r="D19" s="77"/>
@@ -2963,10 +2968,10 @@
       <c r="G19" s="77"/>
       <c r="H19" s="77"/>
       <c r="I19" s="69" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J19" s="88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K19" s="46" t="s">
         <v>21</v>
@@ -2975,7 +2980,7 @@
         <v>21</v>
       </c>
       <c r="M19" s="89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N19" s="46" t="s">
         <v>21</v>
@@ -2987,7 +2992,7 @@
         <v>21</v>
       </c>
       <c r="Q19" s="90" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R19" s="91" t="n">
         <v>13</v>
@@ -2997,7 +3002,7 @@
         <v>18</v>
       </c>
       <c r="U19" s="72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V19" s="55" t="s">
         <v>21</v>
@@ -3012,16 +3017,16 @@
         <v>18</v>
       </c>
       <c r="Z19" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA19" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB19" s="92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC19" s="93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD19" s="42"/>
       <c r="AE19" s="43"/>
@@ -3040,7 +3045,7 @@
       <c r="G20" s="43"/>
       <c r="H20" s="44"/>
       <c r="I20" s="94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J20" s="94"/>
       <c r="K20" s="94"/>
@@ -3050,7 +3055,7 @@
       <c r="O20" s="94"/>
       <c r="P20" s="94"/>
       <c r="Q20" s="95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R20" s="96" t="n">
         <v>14</v>
@@ -3060,10 +3065,10 @@
         <v>17</v>
       </c>
       <c r="U20" s="98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V20" s="99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W20" s="99"/>
       <c r="X20" s="99"/>
@@ -3089,7 +3094,7 @@
       <c r="G21" s="101"/>
       <c r="H21" s="102"/>
       <c r="I21" s="103" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J21" s="103"/>
       <c r="K21" s="103"/>
@@ -3099,7 +3104,7 @@
       <c r="O21" s="103"/>
       <c r="P21" s="103"/>
       <c r="Q21" s="104" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R21" s="105" t="n">
         <v>15</v>
@@ -3109,10 +3114,10 @@
         <v>16</v>
       </c>
       <c r="U21" s="108" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V21" s="109" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W21" s="109"/>
       <c r="X21" s="109"/>
@@ -3131,12 +3136,12 @@
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H23" s="113" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I23" s="113"/>
       <c r="J23" s="113"/>
       <c r="L23" s="114" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M23" s="114"/>
       <c r="N23" s="114"/>
@@ -3144,11 +3149,11 @@
       <c r="P23" s="114"/>
       <c r="Q23" s="114"/>
       <c r="S23" s="113" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T23" s="113"/>
       <c r="W23" s="115" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X23" s="115"/>
       <c r="Y23" s="115"/>
@@ -3160,7 +3165,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H24" s="116" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I24" s="116"/>
       <c r="J24" s="116"/>
@@ -3171,17 +3176,17 @@
       <c r="P24" s="114"/>
       <c r="Q24" s="114"/>
       <c r="S24" s="117" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T24" s="117"/>
       <c r="W24" s="46" t="s">
         <v>21</v>
       </c>
       <c r="X24" s="118" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y24" s="119" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z24" s="119"/>
       <c r="AA24" s="119"/>
@@ -3191,12 +3196,12 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H25" s="120" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I25" s="120"/>
       <c r="J25" s="120"/>
       <c r="L25" s="121" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M25" s="121"/>
       <c r="N25" s="121"/>
@@ -3204,17 +3209,17 @@
       <c r="P25" s="121"/>
       <c r="Q25" s="121"/>
       <c r="S25" s="122" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T25" s="122"/>
       <c r="W25" s="47" t="s">
         <v>17</v>
       </c>
       <c r="X25" s="123" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y25" s="124" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Z25" s="124"/>
       <c r="AA25" s="124"/>
@@ -3224,12 +3229,12 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H26" s="125" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="125"/>
       <c r="J26" s="125"/>
       <c r="L26" s="126" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M26" s="126"/>
       <c r="N26" s="126"/>
@@ -3237,17 +3242,17 @@
       <c r="P26" s="126"/>
       <c r="Q26" s="126"/>
       <c r="S26" s="127" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T26" s="127"/>
       <c r="W26" s="75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X26" s="123" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y26" s="124" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z26" s="124"/>
       <c r="AA26" s="124"/>
@@ -3257,7 +3262,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H27" s="128" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" s="128"/>
       <c r="J27" s="128"/>
@@ -3268,17 +3273,17 @@
       <c r="P27" s="129"/>
       <c r="Q27" s="129"/>
       <c r="S27" s="130" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T27" s="130"/>
       <c r="W27" s="48" t="n">
         <v>0</v>
       </c>
       <c r="X27" s="131" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y27" s="132" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z27" s="132"/>
       <c r="AA27" s="132"/>
@@ -3288,12 +3293,12 @@
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H28" s="133" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="133"/>
       <c r="J28" s="133"/>
       <c r="L28" s="114" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M28" s="114"/>
       <c r="N28" s="114"/>
@@ -3301,7 +3306,7 @@
       <c r="P28" s="114"/>
       <c r="Q28" s="114"/>
       <c r="S28" s="134" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T28" s="134"/>
     </row>
@@ -3313,7 +3318,7 @@
       <c r="P29" s="114"/>
       <c r="Q29" s="114"/>
       <c r="W29" s="115" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X29" s="115"/>
       <c r="Y29" s="115"/>
@@ -3325,7 +3330,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L30" s="135" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M30" s="135"/>
       <c r="N30" s="135"/>
@@ -3336,10 +3341,10 @@
         <v>18</v>
       </c>
       <c r="X30" s="136" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y30" s="124" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Z30" s="124"/>
       <c r="AA30" s="124"/>
@@ -3349,7 +3354,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L31" s="133" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M31" s="133"/>
       <c r="N31" s="133"/>
@@ -3357,13 +3362,13 @@
       <c r="P31" s="133"/>
       <c r="Q31" s="133"/>
       <c r="W31" s="89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X31" s="136" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y31" s="124" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z31" s="124"/>
       <c r="AA31" s="124"/>
@@ -3376,10 +3381,10 @@
         <v>21</v>
       </c>
       <c r="X32" s="136" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y32" s="124" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z32" s="124"/>
       <c r="AA32" s="124"/>
@@ -3393,10 +3398,10 @@
         <v>17</v>
       </c>
       <c r="X33" s="138" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y33" s="132" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z33" s="132"/>
       <c r="AA33" s="132"/>
